--- a/public/file/guru.xlsx
+++ b/public/file/guru.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21126"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84138ED0-929C-47AA-B598-017F54AFD1E9}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{9B824369-C9D8-43FE-A163-AD6BE26CF601}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23256" windowHeight="12108"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="55">
   <si>
     <t>nama</t>
   </si>
@@ -118,12 +112,84 @@
   </si>
   <si>
     <t>muhammadzaki@sekolah.com</t>
+  </si>
+  <si>
+    <t>AHMAD KHAIRANI</t>
+  </si>
+  <si>
+    <t>SATRIAL FITRI</t>
+  </si>
+  <si>
+    <t>agung satria wijaya</t>
+  </si>
+  <si>
+    <t>HABIB</t>
+  </si>
+  <si>
+    <t>Hayati Alexandrina</t>
+  </si>
+  <si>
+    <t>Sri Rahayu</t>
+  </si>
+  <si>
+    <t>ahmadkhairani@gmail.com</t>
+  </si>
+  <si>
+    <t>satrialfitri@gmail.com</t>
+  </si>
+  <si>
+    <t>agung@gmail.com</t>
+  </si>
+  <si>
+    <t>habib@gmail.com</t>
+  </si>
+  <si>
+    <t>hayati@gmail.com</t>
+  </si>
+  <si>
+    <t>srirahayu@gmail.com</t>
+  </si>
+  <si>
+    <t>198007292003122000</t>
+  </si>
+  <si>
+    <t>197910302003122000</t>
+  </si>
+  <si>
+    <t>196909012003121000</t>
+  </si>
+  <si>
+    <t>199401052024211000</t>
+  </si>
+  <si>
+    <t>197510042006041000</t>
+  </si>
+  <si>
+    <t>199202052025211000</t>
+  </si>
+  <si>
+    <t>082383818435</t>
+  </si>
+  <si>
+    <t>085274014675</t>
+  </si>
+  <si>
+    <t>081977524948</t>
+  </si>
+  <si>
+    <t>082385089969</t>
+  </si>
+  <si>
+    <t>081363842444</t>
+  </si>
+  <si>
+    <t>081363435035</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -227,7 +293,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -279,7 +345,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -473,25 +539,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C42BAD2-62CA-4458-96DF-1DAA352D7124}">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -511,7 +577,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -531,7 +597,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -551,7 +617,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -571,7 +637,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -591,7 +657,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -611,7 +677,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -631,7 +697,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -651,16 +717,143 @@
         <v>23</v>
       </c>
     </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9">
+        <v>12345678</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10">
+        <v>12345678</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11">
+        <v>12345678</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12">
+        <v>12345678</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13">
+        <v>12345678</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14">
+        <v>12345678</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{17554BA6-1E7F-4C5C-BF62-4521744EB4AD}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{19A7372F-C08B-494C-9321-771A4B1E0B7E}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{EEEEC9D3-1B96-4F97-8981-EBAE56C18BD7}"/>
-    <hyperlink ref="B5" r:id="rId4" xr:uid="{F11387E9-485E-4018-B001-A095F38A242B}"/>
-    <hyperlink ref="B6" r:id="rId5" xr:uid="{82869BEF-7C10-4545-AA70-B177AF3039B1}"/>
-    <hyperlink ref="B7" r:id="rId6" xr:uid="{77003185-F000-4D95-9CA7-C4E3811A4BDD}"/>
-    <hyperlink ref="B8" r:id="rId7" xr:uid="{4365F502-69C1-4A0E-975F-00A6D54E6A16}"/>
+    <hyperlink ref="B2" r:id="rId1"/>
+    <hyperlink ref="B8" r:id="rId2"/>
+    <hyperlink ref="B7" r:id="rId3"/>
+    <hyperlink ref="B6" r:id="rId4"/>
+    <hyperlink ref="B5" r:id="rId5"/>
+    <hyperlink ref="B4" r:id="rId6"/>
+    <hyperlink ref="B3" r:id="rId7"/>
+    <hyperlink ref="B9" r:id="rId8"/>
+    <hyperlink ref="B10" r:id="rId9"/>
+    <hyperlink ref="B11" r:id="rId10"/>
+    <hyperlink ref="B12" r:id="rId11"/>
+    <hyperlink ref="B13" r:id="rId12"/>
+    <hyperlink ref="B14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId14"/>
 </worksheet>
 </file>